--- a/data/data_UserCost_集計加工用.xlsx
+++ b/data/data_UserCost_集計加工用.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE875E6-7D6E-48AC-8EAC-EB25CC8050A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF8481B-9188-4CD8-9687-E555F712859E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1E8CBEA0-B07E-43F0-9BA1-B7E249EDD9BE}"/>
   </bookViews>
@@ -23,8 +23,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
   <si>
     <t>I</t>
     <phoneticPr fontId="1"/>
@@ -114,6 +112,14 @@
   </si>
   <si>
     <t>NA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JIP_UC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SNA_UC</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -535,13 +541,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC9D2112-8441-4E07-A3B1-B194ED639F13}">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
@@ -581,1772 +587,2026 @@
       <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1994</v>
       </c>
       <c r="B2">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>623503.9</v>
       </c>
       <c r="C2">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>89003.3</v>
       </c>
       <c r="D2">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>74650.899999999994</v>
       </c>
       <c r="E2">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>119.2</v>
       </c>
       <c r="F2">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>521675.1</v>
       </c>
       <c r="G2">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>464267.4</v>
       </c>
       <c r="H2">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>112.4</v>
       </c>
       <c r="I2">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>261625.60000000001</v>
       </c>
       <c r="J2">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5356.5</v>
       </c>
       <c r="K2">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1909.1</v>
       </c>
       <c r="L2">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>4.3633333333333324</v>
       </c>
       <c r="M2">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>66.801580408687755</v>
       </c>
       <c r="N2" t="str">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>NA</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>139.42877195326787</v>
+      </c>
+      <c r="P2">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>115.91812216510095</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1995</v>
       </c>
       <c r="B3">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>633070.19999999995</v>
       </c>
       <c r="C3">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>91924.2</v>
       </c>
       <c r="D3">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>78359.3</v>
       </c>
       <c r="E3">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>117.3</v>
       </c>
       <c r="F3">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>530463.19999999995</v>
       </c>
       <c r="G3">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>475140.8</v>
       </c>
       <c r="H3">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>111.6</v>
       </c>
       <c r="I3">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>266004.09999999998</v>
       </c>
       <c r="J3">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5379.5</v>
       </c>
       <c r="K3">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1911.6</v>
       </c>
       <c r="L3">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>3.4434999999999998</v>
       </c>
       <c r="M3">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>69.36932371914088</v>
       </c>
       <c r="N3">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>13.208882895519983</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O3">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>139.50705134088565</v>
+      </c>
+      <c r="P3">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>116.59329094382416</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1996</v>
       </c>
       <c r="B4">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>652745.4</v>
       </c>
       <c r="C4">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>96951.9</v>
       </c>
       <c r="D4">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>83554.8</v>
       </c>
       <c r="E4">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>116</v>
       </c>
       <c r="F4">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>546227.9</v>
       </c>
       <c r="G4">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>489753.59999999998</v>
       </c>
       <c r="H4">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>111.5</v>
       </c>
       <c r="I4">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>270691.5</v>
       </c>
       <c r="J4">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5419</v>
       </c>
       <c r="K4">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1914.8</v>
       </c>
       <c r="L4">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>3.1014999999999997</v>
       </c>
       <c r="M4">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>70.614734744674337</v>
       </c>
       <c r="N4">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>12.206655754764631</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O4">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>142.60047858824123</v>
+      </c>
+      <c r="P4">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>118.77844082873577</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1997</v>
       </c>
       <c r="B5">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>672576.7</v>
       </c>
       <c r="C5">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>99717.6</v>
       </c>
       <c r="D5">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>86803</v>
       </c>
       <c r="E5">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>114.9</v>
       </c>
       <c r="F5">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>554111.80000000005</v>
       </c>
       <c r="G5">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>496428.79999999999</v>
       </c>
       <c r="H5">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>111.6</v>
       </c>
       <c r="I5">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>278752.5</v>
       </c>
       <c r="J5">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5469.7</v>
       </c>
       <c r="K5">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1887.1</v>
       </c>
       <c r="L5">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>2.3736666666666664</v>
       </c>
       <c r="M5">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>69.792998326645943</v>
       </c>
       <c r="N5">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>12.238508306607759</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O5">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>137.1518766702539</v>
+      </c>
+      <c r="P5">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>114.73486845321035</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1998</v>
       </c>
       <c r="B6">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>683061</v>
       </c>
       <c r="C6">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>94245.8</v>
       </c>
       <c r="D6">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>83086</v>
       </c>
       <c r="E6">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>113.4</v>
       </c>
       <c r="F6">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>543304</v>
       </c>
       <c r="G6">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>487628.9</v>
       </c>
       <c r="H6">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>111.4</v>
       </c>
       <c r="I6">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>274573.3</v>
       </c>
       <c r="J6">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5425.5</v>
       </c>
       <c r="K6">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1866.5</v>
       </c>
       <c r="L6">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.5414166666666667</v>
       </c>
       <c r="M6">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>74.795047140603103</v>
       </c>
       <c r="N6">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>12.45382125191075</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>132.52291195854036</v>
+      </c>
+      <c r="P6">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>108.89329627455095</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1999</v>
       </c>
       <c r="B7">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>690962.4</v>
       </c>
       <c r="C7">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>87750.6</v>
       </c>
       <c r="D7">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>78994.3</v>
       </c>
       <c r="E7">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>111.1</v>
       </c>
       <c r="F7">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>534107.1</v>
       </c>
       <c r="G7">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>485933.9</v>
       </c>
       <c r="H7">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>109.9</v>
       </c>
       <c r="I7">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>269253.2</v>
       </c>
       <c r="J7">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5368.7</v>
       </c>
       <c r="K7">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1850.9</v>
       </c>
       <c r="L7">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.7489999999999999</v>
       </c>
       <c r="M7">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>76.159037577065462</v>
       </c>
       <c r="N7">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.689907636360436</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>138.05374210611262</v>
+      </c>
+      <c r="P7">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>106.85169487578641</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2000</v>
       </c>
       <c r="B8">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>701749.3</v>
       </c>
       <c r="C8">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>93225.3</v>
       </c>
       <c r="D8">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>84580.9</v>
       </c>
       <c r="E8">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>110.2</v>
       </c>
       <c r="F8">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>543394.80000000005</v>
       </c>
       <c r="G8">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>500406.6</v>
       </c>
       <c r="H8">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>108.6</v>
       </c>
       <c r="I8">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>269891.90000000002</v>
       </c>
       <c r="J8">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5374.6</v>
       </c>
       <c r="K8">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1858.5</v>
       </c>
       <c r="L8">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.7444166666666667</v>
       </c>
       <c r="M8">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>74.67910291046482</v>
       </c>
       <c r="N8">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.930953116985819</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O8">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>136.45259586783763</v>
+      </c>
+      <c r="P8">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>109.76496758864</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2001</v>
       </c>
       <c r="B9">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>710804.9</v>
       </c>
       <c r="C9">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>91053.1</v>
       </c>
       <c r="D9">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>84581.6</v>
       </c>
       <c r="E9">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>107.7</v>
       </c>
       <c r="F9">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>539441.6</v>
       </c>
       <c r="G9">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>501830.8</v>
       </c>
       <c r="H9">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>107.5</v>
       </c>
       <c r="I9">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>266607.5</v>
       </c>
       <c r="J9">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5391.9</v>
       </c>
       <c r="K9">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1843.1</v>
       </c>
       <c r="L9">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.319</v>
       </c>
       <c r="M9">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>83.347312779357821</v>
       </c>
       <c r="N9">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.684728435069331</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O9">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>130.96654639043743</v>
+      </c>
+      <c r="P9">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>106.52618807197598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2002</v>
       </c>
       <c r="B10">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>713480.3</v>
       </c>
       <c r="C10">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>84640.2</v>
       </c>
       <c r="D10">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>80298.3</v>
       </c>
       <c r="E10">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>105.4</v>
       </c>
       <c r="F10">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>532390.80000000005</v>
       </c>
       <c r="G10">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>502257.3</v>
       </c>
       <c r="H10">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>106</v>
       </c>
       <c r="I10">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>257436.79999999999</v>
       </c>
       <c r="J10">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5352.4</v>
       </c>
       <c r="K10">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1830.6</v>
       </c>
       <c r="L10">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.2631666666666665</v>
       </c>
       <c r="M10">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>84.175727827213876</v>
       </c>
       <c r="N10">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.531265471017424</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O10">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>128.67925922409717</v>
+      </c>
+      <c r="P10">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>109.04434576480895</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2003</v>
       </c>
       <c r="B11">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>716599</v>
       </c>
       <c r="C11">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>83039.7</v>
       </c>
       <c r="D11">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>80787.3</v>
       </c>
       <c r="E11">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>102.8</v>
       </c>
       <c r="F11">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>530211.80000000005</v>
       </c>
       <c r="G11">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>509189</v>
       </c>
       <c r="H11">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>104.1</v>
       </c>
       <c r="I11">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>255183.6</v>
       </c>
       <c r="J11">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5369.6</v>
       </c>
       <c r="K11">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1834.2</v>
       </c>
       <c r="L11">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.00325</v>
       </c>
       <c r="M11">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>73.720975996733998</v>
       </c>
       <c r="N11">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.201570667052755</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O11">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>122.02201318005157</v>
+      </c>
+      <c r="P11">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>110.48406112166347</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2004</v>
       </c>
       <c r="B12">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>722919.2</v>
       </c>
       <c r="C12">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>83687.100000000006</v>
       </c>
       <c r="D12">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>82738.3</v>
       </c>
       <c r="E12">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>101.1</v>
       </c>
       <c r="F12">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>534634.1</v>
       </c>
       <c r="G12">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>519947.9</v>
       </c>
       <c r="H12">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>102.8</v>
       </c>
       <c r="I12">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>256593.3</v>
       </c>
       <c r="J12">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5404.3</v>
       </c>
       <c r="K12">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1842.7</v>
       </c>
       <c r="L12">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.4926666666666666</v>
       </c>
       <c r="M12">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>66.741303875393172</v>
       </c>
       <c r="N12">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>10.796400776445408</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O12">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>122.84082339794899</v>
+      </c>
+      <c r="P12">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>111.52845423737099</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2005</v>
       </c>
       <c r="B13">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>733117.8</v>
       </c>
       <c r="C13">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>89354</v>
       </c>
       <c r="D13">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>88812.1</v>
       </c>
       <c r="E13">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100.6</v>
       </c>
       <c r="F13">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>537385.19999999995</v>
       </c>
       <c r="G13">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>529558</v>
       </c>
       <c r="H13">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>101.5</v>
       </c>
       <c r="I13">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>261326.4</v>
       </c>
       <c r="J13">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5466.8</v>
       </c>
       <c r="K13">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1830.5</v>
       </c>
       <c r="L13">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.3547499999999999</v>
       </c>
       <c r="M13">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>64.058618712584206</v>
       </c>
       <c r="N13">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>10.949411773819246</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O13">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>119.48426415799334</v>
+      </c>
+      <c r="P13">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>109.66542008562612</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2006</v>
       </c>
       <c r="B14">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>744573.5</v>
       </c>
       <c r="C14">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>91710.1</v>
       </c>
       <c r="D14">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>90929.3</v>
       </c>
       <c r="E14">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100.9</v>
       </c>
       <c r="F14">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>540566</v>
       </c>
       <c r="G14">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>537746.6</v>
       </c>
       <c r="H14">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100.5</v>
       </c>
       <c r="I14">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>266138.09999999998</v>
       </c>
       <c r="J14">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5570.5</v>
       </c>
       <c r="K14">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1837.3</v>
       </c>
       <c r="L14">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.7404999999999999</v>
       </c>
       <c r="M14">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>50.535091860347052</v>
       </c>
       <c r="N14">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>10.94699924077686</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O14">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>127.96440634732191</v>
+      </c>
+      <c r="P14">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>105.25223764160587</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2007</v>
       </c>
       <c r="B15">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>755589.5</v>
       </c>
       <c r="C15">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>92758.7</v>
       </c>
       <c r="D15">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>92376.5</v>
       </c>
       <c r="E15">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100.4</v>
       </c>
       <c r="F15">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>544571.1</v>
       </c>
       <c r="G15">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>547040.9</v>
       </c>
       <c r="H15">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>99.5</v>
       </c>
       <c r="I15">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>267694.3</v>
       </c>
       <c r="J15">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5643.5</v>
       </c>
       <c r="K15">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1826.7</v>
       </c>
       <c r="L15">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.6655</v>
       </c>
       <c r="M15">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>45.586588501095854</v>
       </c>
       <c r="N15">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>10.978459480494532</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O15">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>130.01431166091476</v>
+      </c>
+      <c r="P15">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>104.82424166365161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2008</v>
       </c>
       <c r="B16">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>761944.2</v>
       </c>
       <c r="C16">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>90952.9</v>
       </c>
       <c r="D16">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>89951.7</v>
       </c>
       <c r="E16">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>101.1</v>
       </c>
       <c r="F16">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>533355.4</v>
       </c>
       <c r="G16">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>540659</v>
       </c>
       <c r="H16">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98.6</v>
       </c>
       <c r="I16">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>267968.90000000002</v>
       </c>
       <c r="J16">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5665.1</v>
       </c>
       <c r="K16">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1805.3</v>
       </c>
       <c r="L16">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.4673333333333334</v>
       </c>
       <c r="M16">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>48.12649710260915</v>
       </c>
       <c r="N16">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.196317577202974</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O16">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>130.87576816991893</v>
+      </c>
+      <c r="P16">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>96.279386507683114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2009</v>
       </c>
       <c r="B17">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>754070.8</v>
       </c>
       <c r="C17">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>77307.600000000006</v>
       </c>
       <c r="D17">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>78443.3</v>
       </c>
       <c r="E17">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98.6</v>
       </c>
       <c r="F17">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>499361.7</v>
       </c>
       <c r="G17">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>508565.8</v>
       </c>
       <c r="H17">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98.2</v>
       </c>
       <c r="I17">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>254795.6</v>
       </c>
       <c r="J17">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5625.6</v>
       </c>
       <c r="K17">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1756.8</v>
       </c>
       <c r="L17">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.33375</v>
       </c>
       <c r="M17">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>50.48465613639442</v>
       </c>
       <c r="N17">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.17942757488014</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O17">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>129.56962937735909</v>
+      </c>
+      <c r="P17">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>85.45146131530376</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2010</v>
       </c>
       <c r="B18">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>745677.4</v>
       </c>
       <c r="C18">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>75167.100000000006</v>
       </c>
       <c r="D18">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>77118</v>
       </c>
       <c r="E18">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>97.5</v>
       </c>
       <c r="F18">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>510139.6</v>
       </c>
       <c r="G18">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>529602.4</v>
       </c>
       <c r="H18">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>96.3</v>
       </c>
       <c r="I18">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>252304.1</v>
       </c>
       <c r="J18">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5647</v>
       </c>
       <c r="K18">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1775.2</v>
       </c>
       <c r="L18">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.1483333333333332</v>
       </c>
       <c r="M18">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>49.823310060131874</v>
       </c>
       <c r="N18">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.081253908784161</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>125.62660648178718</v>
+      </c>
+      <c r="P18">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>93.836355652097652</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2011</v>
       </c>
       <c r="B19">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>737122.5</v>
       </c>
       <c r="C19">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>76572.7</v>
       </c>
       <c r="D19">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>79139.399999999994</v>
       </c>
       <c r="E19">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>96.8</v>
       </c>
       <c r="F19">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>501142</v>
       </c>
       <c r="G19">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>528541.30000000005</v>
       </c>
       <c r="H19">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>94.8</v>
       </c>
       <c r="I19">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>252732.3</v>
       </c>
       <c r="J19">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5647.7</v>
       </c>
       <c r="K19">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1770.2</v>
       </c>
       <c r="L19">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1.1024166666666666</v>
       </c>
       <c r="M19">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>50.325053016775641</v>
       </c>
       <c r="N19">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.41614322762095</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O19">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>114.48357513919221</v>
+      </c>
+      <c r="P19">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>89.013065480280829</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2012</v>
       </c>
       <c r="B20">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>735926.4</v>
       </c>
       <c r="C20">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>79409.3</v>
       </c>
       <c r="D20">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>82412.600000000006</v>
       </c>
       <c r="E20">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>96.4</v>
       </c>
       <c r="F20">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>505377.1</v>
       </c>
       <c r="G20">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>537256.6</v>
       </c>
       <c r="H20">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>94.1</v>
       </c>
       <c r="I20">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>252878.7</v>
       </c>
       <c r="J20">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5629.3</v>
       </c>
       <c r="K20">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1782.3</v>
       </c>
       <c r="L20">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>0.83558333333333323</v>
       </c>
       <c r="M20">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>49.51410606061431</v>
       </c>
       <c r="N20">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>10.9351430732341</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O20">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>108.20135379013169</v>
+      </c>
+      <c r="P20">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>90.613773986333214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2013</v>
       </c>
       <c r="B21">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>735587.2</v>
       </c>
       <c r="C21">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>81868</v>
       </c>
       <c r="D21">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>84303.3</v>
       </c>
       <c r="E21">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>97.1</v>
       </c>
       <c r="F21">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>514553.3</v>
       </c>
       <c r="G21">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>547987.1</v>
       </c>
       <c r="H21">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>93.9</v>
       </c>
       <c r="I21">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>254642.2</v>
       </c>
       <c r="J21">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5668.8</v>
       </c>
       <c r="K21">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1763</v>
       </c>
       <c r="L21">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>0.68966666666666676</v>
       </c>
       <c r="M21">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>42.860782477943289</v>
       </c>
       <c r="N21">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.17057357909705</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O21">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>106.43526576315357</v>
+      </c>
+      <c r="P21">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>94.105427948075331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2014</v>
       </c>
       <c r="B22">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>740014.3</v>
       </c>
       <c r="C22">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>88612.800000000003</v>
       </c>
       <c r="D22">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>90047</v>
       </c>
       <c r="E22">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98.4</v>
       </c>
       <c r="F22">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>528215.6</v>
       </c>
       <c r="G22">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>552951.4</v>
       </c>
       <c r="H22">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>95.5</v>
       </c>
       <c r="I22">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>258856</v>
       </c>
       <c r="J22">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5701.8</v>
       </c>
       <c r="K22">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1758.4</v>
       </c>
       <c r="L22">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>0.52033333333333331</v>
       </c>
       <c r="M22">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>36.749755343255814</v>
       </c>
       <c r="N22">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.444693436753651</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O22">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>101.34425778320755</v>
+      </c>
+      <c r="P22">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>93.739947528383681</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2015</v>
       </c>
       <c r="B23">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>748231.3</v>
       </c>
       <c r="C23">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>94492</v>
       </c>
       <c r="D23">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>95206.399999999994</v>
       </c>
       <c r="E23">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>99.2</v>
       </c>
       <c r="F23">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>548866.69999999995</v>
       </c>
       <c r="G23">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>562904.4</v>
       </c>
       <c r="H23">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>97.5</v>
       </c>
       <c r="I23">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>261384.7</v>
       </c>
       <c r="J23">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5733.9</v>
       </c>
       <c r="K23">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1752.4</v>
       </c>
       <c r="L23">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>0.34999999999999992</v>
       </c>
       <c r="M23">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>34.106402455974845</v>
       </c>
       <c r="N23">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.658558490018368</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="P23">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2016</v>
       </c>
       <c r="B24">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>755926.3</v>
       </c>
       <c r="C24">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>94146</v>
       </c>
       <c r="D24">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>95386.2</v>
       </c>
       <c r="E24">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98.7</v>
       </c>
       <c r="F24">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>555970.6</v>
       </c>
       <c r="G24">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>566872.80000000005</v>
       </c>
       <c r="H24">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98.1</v>
       </c>
       <c r="I24">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>266925.7</v>
       </c>
       <c r="J24">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5812.4</v>
       </c>
       <c r="K24">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1743.9</v>
       </c>
       <c r="L24">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>-6.6249999999999989E-2</v>
       </c>
       <c r="M24">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>31.155451964405234</v>
       </c>
       <c r="N24">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.554047525143627</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O24">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>99.344337384201467</v>
+      </c>
+      <c r="P24">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>98.736250140436212</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2017</v>
       </c>
       <c r="B25">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>763930.4</v>
       </c>
       <c r="C25">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>97331.7</v>
       </c>
       <c r="D25">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>97848.9</v>
       </c>
       <c r="E25">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>99.5</v>
       </c>
       <c r="F25">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>565119</v>
       </c>
       <c r="G25">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>576075.69999999995</v>
       </c>
       <c r="H25">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98.1</v>
       </c>
       <c r="I25">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>271000.40000000002</v>
       </c>
       <c r="J25">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5876</v>
       </c>
       <c r="K25">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1745.1</v>
       </c>
       <c r="L25">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5.1666666666666673E-2</v>
       </c>
       <c r="M25">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>28.321250452807572</v>
       </c>
       <c r="N25">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.816972104291116</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O25">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>101.22243190969431</v>
+      </c>
+      <c r="P25">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>99.671156403377509</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2018</v>
       </c>
       <c r="B26">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>774702.1</v>
       </c>
       <c r="C26">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100849.3</v>
       </c>
       <c r="D26">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100844</v>
       </c>
       <c r="E26">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100</v>
       </c>
       <c r="F26">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>569153.5</v>
       </c>
       <c r="G26">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>580881</v>
       </c>
       <c r="H26">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98</v>
       </c>
       <c r="I26">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>279905.7</v>
       </c>
       <c r="J26">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>5989.5</v>
       </c>
       <c r="K26">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1727.8</v>
       </c>
       <c r="L26">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>6.4999999999999988E-2</v>
       </c>
       <c r="M26">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>26.802017505469603</v>
       </c>
       <c r="N26">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>11.791335964637629</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>95.316104339729804</v>
+      </c>
+      <c r="P26">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>94.964544032083779</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2019</v>
       </c>
       <c r="B27">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>783363.9</v>
       </c>
       <c r="C27">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>101949.7</v>
       </c>
       <c r="D27">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>101731.7</v>
       </c>
       <c r="E27">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100.2</v>
       </c>
       <c r="F27">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>571838</v>
       </c>
       <c r="G27">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>579089</v>
       </c>
       <c r="H27">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>98.7</v>
       </c>
       <c r="I27">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>284889.7</v>
       </c>
       <c r="J27">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>6058.6</v>
       </c>
       <c r="K27">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1696.6</v>
       </c>
       <c r="L27">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>-0.11041666666666666</v>
       </c>
       <c r="M27">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>26.758976214554316</v>
       </c>
       <c r="N27">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>12.04177709083271</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O27">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>91.40435369661823</v>
+      </c>
+      <c r="P27">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>90.793758484333352</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2020</v>
       </c>
       <c r="B28">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>785491.9</v>
       </c>
       <c r="C28">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>97037.4</v>
       </c>
       <c r="D28">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>97037.4</v>
       </c>
       <c r="E28">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100</v>
       </c>
       <c r="F28">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>554074.4</v>
       </c>
       <c r="G28">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>554285</v>
       </c>
       <c r="H28">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100</v>
       </c>
       <c r="I28">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>281114.40000000002</v>
       </c>
       <c r="J28">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>6033.3</v>
       </c>
       <c r="K28">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1659.7</v>
       </c>
       <c r="L28">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>-5.4166666666666634E-3</v>
       </c>
       <c r="M28">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>27.403658291459656</v>
       </c>
       <c r="N28">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>12.115620850028961</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O28">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>91.346076984611273</v>
+      </c>
+      <c r="P28">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>80.967273510427304</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2021</v>
       </c>
       <c r="B29">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>789000.5</v>
       </c>
       <c r="C29">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100800.9</v>
       </c>
       <c r="D29">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>99381.3</v>
       </c>
       <c r="E29">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>101.4</v>
       </c>
       <c r="F29">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>573568.80000000005</v>
       </c>
       <c r="G29">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>574040.80000000005</v>
       </c>
       <c r="H29">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>99.9</v>
       </c>
       <c r="I29">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>287685.3</v>
       </c>
       <c r="J29">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>6051.2</v>
       </c>
       <c r="K29">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1678.4</v>
       </c>
       <c r="L29">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>7.166666666666667E-2</v>
       </c>
       <c r="M29">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>27.177147456032884</v>
       </c>
       <c r="N29">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>12.386162097915975</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O29" t="str">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>NA</v>
+      </c>
+      <c r="P29">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>83.393679494370261</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2022</v>
       </c>
       <c r="B30">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>794844.7</v>
       </c>
       <c r="C30">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>107813.7</v>
       </c>
       <c r="D30">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>102455.3</v>
       </c>
       <c r="E30">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>105.2</v>
       </c>
       <c r="F30">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>584900.6</v>
       </c>
       <c r="G30">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>581685</v>
       </c>
       <c r="H30">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>100.6</v>
       </c>
       <c r="I30">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>295447.40000000002</v>
       </c>
       <c r="J30">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>6086.3</v>
       </c>
       <c r="K30">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1675.5</v>
       </c>
       <c r="L30">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>0.23166666666666666</v>
       </c>
       <c r="M30">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>27.028655841924593</v>
       </c>
       <c r="N30">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>12.923882811227621</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O30" t="str">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>NA</v>
+      </c>
+      <c r="P30">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>83.722017532311483</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2023</v>
       </c>
       <c r="B31">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>801669.7</v>
       </c>
       <c r="C31">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>113786.1</v>
       </c>
       <c r="D31">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>104246.7</v>
       </c>
       <c r="E31">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>109.2</v>
       </c>
       <c r="F31">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>616033</v>
       </c>
       <c r="G31">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>585877.69999999995</v>
       </c>
       <c r="H31">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>105.1</v>
       </c>
       <c r="I31">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>300547</v>
       </c>
       <c r="J31">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>6129.3</v>
       </c>
       <c r="K31">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1677.9</v>
       </c>
       <c r="L31">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>0.56250000000000011</v>
       </c>
       <c r="M31">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>27.172550470504312</v>
       </c>
       <c r="N31">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>13.456855156736905</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O31" t="str">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>NA</v>
+      </c>
+      <c r="P31">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>97.891785162845878</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2024</v>
       </c>
       <c r="B32">
-        <f>HLOOKUP(B$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(B$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>820134.40000000002</v>
       </c>
       <c r="C32">
-        <f>HLOOKUP(C$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(C$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>117611.9</v>
       </c>
       <c r="D32">
-        <f>HLOOKUP(D$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(D$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>104104.9</v>
       </c>
       <c r="E32">
-        <f>HLOOKUP(E$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(E$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>113</v>
       </c>
       <c r="F32">
-        <f>HLOOKUP(F$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(F$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>634226</v>
       </c>
       <c r="G32">
-        <f>HLOOKUP(G$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(G$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>584471.1</v>
       </c>
       <c r="H32">
-        <f>HLOOKUP(H$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(H$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>108.5</v>
       </c>
       <c r="I32">
-        <f>HLOOKUP(I$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(I$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>311663</v>
       </c>
       <c r="J32">
-        <f>HLOOKUP(J$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(J$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>6184.2</v>
       </c>
       <c r="K32">
-        <f>HLOOKUP(K$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(K$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>1661.5</v>
       </c>
       <c r="L32">
-        <f>HLOOKUP(L$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(L$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>0.91833333333333345</v>
       </c>
       <c r="M32">
-        <f>HLOOKUP(M$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(M$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>25.957248065412493</v>
       </c>
       <c r="N32">
-        <f>HLOOKUP(N$1,Sheet1!$B$1:$Q$36,ROW()+4,FALSE)</f>
+        <f>HLOOKUP(N$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
         <v>12.367587299357822</v>
+      </c>
+      <c r="O32" t="str">
+        <f>HLOOKUP(O$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>NA</v>
+      </c>
+      <c r="P32" t="str">
+        <f>HLOOKUP(P$1,Sheet1!$B$1:$S$36,ROW()+4,FALSE)</f>
+        <v>NA</v>
       </c>
     </row>
   </sheetData>
@@ -2359,7 +2619,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC8F5B2A-CCCB-467A-B37B-6E0DDC07FCBA}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="5" width="8.88671875" style="1"/>
@@ -2367,10 +2627,10 @@
     <col min="7" max="14" width="8.88671875" style="1"/>
     <col min="15" max="15" width="11.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.88671875" style="1"/>
+    <col min="17" max="19" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>11</v>
       </c>
@@ -2419,8 +2679,14 @@
       <c r="Q1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="N2" s="1">
         <f t="shared" ref="N2:N36" si="0">O2/P2*100</f>
         <v>53.865134524238009</v>
@@ -2432,7 +2698,7 @@
         <v>38084884</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="N3" s="1">
         <f t="shared" si="0"/>
         <v>57.010249717271236</v>
@@ -2444,7 +2710,7 @@
         <v>32763733</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="N4" s="1">
         <f t="shared" si="0"/>
         <v>67.616829363455295</v>
@@ -2456,7 +2722,7 @@
         <v>24087138</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="N5" s="1">
         <f t="shared" si="0"/>
         <v>79.482062119210667</v>
@@ -2468,7 +2734,7 @@
         <v>18251069</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1994</v>
       </c>
@@ -2522,11 +2788,17 @@
       <c r="Q6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S6" t="s">
+      <c r="R6" s="1">
+        <v>139.42877195326787</v>
+      </c>
+      <c r="S6" s="1">
+        <v>115.91812216510095</v>
+      </c>
+      <c r="U6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1995</v>
       </c>
@@ -2581,11 +2853,17 @@
         <f>(B6+C7-B7)/B6*100</f>
         <v>13.208882895519983</v>
       </c>
-      <c r="S7" t="s">
+      <c r="R7" s="1">
+        <v>139.50705134088565</v>
+      </c>
+      <c r="S7" s="1">
+        <v>116.59329094382416</v>
+      </c>
+      <c r="U7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1996</v>
       </c>
@@ -2640,8 +2918,14 @@
         <f t="shared" ref="Q8:Q36" si="2">(B7+C8-B8)/B7*100</f>
         <v>12.206655754764631</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R8" s="1">
+        <v>142.60047858824123</v>
+      </c>
+      <c r="S8" s="1">
+        <v>118.77844082873577</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1997</v>
       </c>
@@ -2696,8 +2980,14 @@
         <f t="shared" si="2"/>
         <v>12.238508306607759</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R9" s="1">
+        <v>137.1518766702539</v>
+      </c>
+      <c r="S9" s="1">
+        <v>114.73486845321035</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1998</v>
       </c>
@@ -2752,8 +3042,14 @@
         <f t="shared" si="2"/>
         <v>12.45382125191075</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R10" s="1">
+        <v>132.52291195854036</v>
+      </c>
+      <c r="S10" s="1">
+        <v>108.89329627455095</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1999</v>
       </c>
@@ -2808,9 +3104,15 @@
         <f t="shared" si="2"/>
         <v>11.689907636360436</v>
       </c>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R11" s="1">
+        <v>138.05374210611262</v>
+      </c>
+      <c r="S11" s="1">
+        <v>106.85169487578641</v>
+      </c>
+      <c r="U11" s="2"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2000</v>
       </c>
@@ -2865,8 +3167,14 @@
         <f t="shared" si="2"/>
         <v>11.930953116985819</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R12" s="1">
+        <v>136.45259586783763</v>
+      </c>
+      <c r="S12" s="1">
+        <v>109.76496758864</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2001</v>
       </c>
@@ -2921,8 +3229,14 @@
         <f t="shared" si="2"/>
         <v>11.684728435069331</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R13" s="1">
+        <v>130.96654639043743</v>
+      </c>
+      <c r="S13" s="1">
+        <v>106.52618807197598</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2002</v>
       </c>
@@ -2977,8 +3291,14 @@
         <f t="shared" si="2"/>
         <v>11.531265471017424</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R14" s="1">
+        <v>128.67925922409717</v>
+      </c>
+      <c r="S14" s="1">
+        <v>109.04434576480895</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2003</v>
       </c>
@@ -3033,8 +3353,14 @@
         <f t="shared" si="2"/>
         <v>11.201570667052755</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="1">
+        <v>122.02201318005157</v>
+      </c>
+      <c r="S15" s="1">
+        <v>110.48406112166347</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2004</v>
       </c>
@@ -3089,8 +3415,14 @@
         <f t="shared" si="2"/>
         <v>10.796400776445408</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="1">
+        <v>122.84082339794899</v>
+      </c>
+      <c r="S16" s="1">
+        <v>111.52845423737099</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2005</v>
       </c>
@@ -3145,8 +3477,14 @@
         <f t="shared" si="2"/>
         <v>10.949411773819246</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="1">
+        <v>119.48426415799334</v>
+      </c>
+      <c r="S17" s="1">
+        <v>109.66542008562612</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2006</v>
       </c>
@@ -3201,8 +3539,14 @@
         <f t="shared" si="2"/>
         <v>10.94699924077686</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="1">
+        <v>127.96440634732191</v>
+      </c>
+      <c r="S18" s="1">
+        <v>105.25223764160587</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2007</v>
       </c>
@@ -3257,8 +3601,14 @@
         <f t="shared" si="2"/>
         <v>10.978459480494532</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="1">
+        <v>130.01431166091476</v>
+      </c>
+      <c r="S19" s="1">
+        <v>104.82424166365161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2008</v>
       </c>
@@ -3313,8 +3663,14 @@
         <f t="shared" si="2"/>
         <v>11.196317577202974</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20" s="1">
+        <v>130.87576816991893</v>
+      </c>
+      <c r="S20" s="1">
+        <v>96.279386507683114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2009</v>
       </c>
@@ -3369,8 +3725,14 @@
         <f t="shared" si="2"/>
         <v>11.17942757488014</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R21" s="1">
+        <v>129.56962937735909</v>
+      </c>
+      <c r="S21" s="1">
+        <v>85.45146131530376</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2010</v>
       </c>
@@ -3425,8 +3787,14 @@
         <f t="shared" si="2"/>
         <v>11.081253908784161</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22" s="1">
+        <v>125.62660648178718</v>
+      </c>
+      <c r="S22" s="1">
+        <v>93.836355652097652</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2011</v>
       </c>
@@ -3481,8 +3849,14 @@
         <f t="shared" si="2"/>
         <v>11.41614322762095</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="1">
+        <v>114.48357513919221</v>
+      </c>
+      <c r="S23" s="1">
+        <v>89.013065480280829</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2012</v>
       </c>
@@ -3537,8 +3911,14 @@
         <f t="shared" si="2"/>
         <v>10.9351430732341</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24" s="1">
+        <v>108.20135379013169</v>
+      </c>
+      <c r="S24" s="1">
+        <v>90.613773986333214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2013</v>
       </c>
@@ -3593,8 +3973,14 @@
         <f t="shared" si="2"/>
         <v>11.17057357909705</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25" s="1">
+        <v>106.43526576315357</v>
+      </c>
+      <c r="S25" s="1">
+        <v>94.105427948075331</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2014</v>
       </c>
@@ -3649,8 +4035,14 @@
         <f t="shared" si="2"/>
         <v>11.444693436753651</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R26" s="1">
+        <v>101.34425778320755</v>
+      </c>
+      <c r="S26" s="1">
+        <v>93.739947528383681</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2015</v>
       </c>
@@ -3705,8 +4097,14 @@
         <f t="shared" si="2"/>
         <v>11.658558490018368</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R27" s="1">
+        <v>100</v>
+      </c>
+      <c r="S27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2016</v>
       </c>
@@ -3761,8 +4159,14 @@
         <f t="shared" si="2"/>
         <v>11.554047525143627</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R28" s="1">
+        <v>99.344337384201467</v>
+      </c>
+      <c r="S28" s="1">
+        <v>98.736250140436212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2017</v>
       </c>
@@ -3817,8 +4221,14 @@
         <f t="shared" si="2"/>
         <v>11.816972104291116</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R29" s="1">
+        <v>101.22243190969431</v>
+      </c>
+      <c r="S29" s="1">
+        <v>99.671156403377509</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2018</v>
       </c>
@@ -3873,8 +4283,14 @@
         <f t="shared" si="2"/>
         <v>11.791335964637629</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R30" s="1">
+        <v>95.316104339729804</v>
+      </c>
+      <c r="S30" s="1">
+        <v>94.964544032083779</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2019</v>
       </c>
@@ -3929,8 +4345,14 @@
         <f t="shared" si="2"/>
         <v>12.04177709083271</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R31" s="1">
+        <v>91.40435369661823</v>
+      </c>
+      <c r="S31" s="1">
+        <v>90.793758484333352</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2020</v>
       </c>
@@ -3985,8 +4407,14 @@
         <f t="shared" si="2"/>
         <v>12.115620850028961</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R32" s="1">
+        <v>91.346076984611273</v>
+      </c>
+      <c r="S32" s="1">
+        <v>80.967273510427304</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2021</v>
       </c>
@@ -4041,8 +4469,14 @@
         <f t="shared" si="2"/>
         <v>12.386162097915975</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S33" s="1">
+        <v>83.393679494370261</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2022</v>
       </c>
@@ -4097,8 +4531,14 @@
         <f t="shared" si="2"/>
         <v>12.923882811227621</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S34" s="1">
+        <v>83.722017532311483</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2023</v>
       </c>
@@ -4153,8 +4593,14 @@
         <f t="shared" si="2"/>
         <v>13.456855156736905</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S35" s="1">
+        <v>97.891785162845878</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2024</v>
       </c>
@@ -4209,8 +4655,14 @@
         <f t="shared" si="2"/>
         <v>12.367587299357822</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2025</v>
       </c>
@@ -4218,57 +4670,57 @@
         <v>1.553333333333333</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2027</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2028</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2029</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2030</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2031</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2032</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2033</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2034</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2035</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2036</v>
       </c>

--- a/data/data_UserCost_集計加工用.xlsx
+++ b/data/data_UserCost_集計加工用.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF8481B-9188-4CD8-9687-E555F712859E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DA9D3E-578D-4744-B49A-365F69EA3E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1E8CBEA0-B07E-43F0-9BA1-B7E249EDD9BE}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>I</t>
     <phoneticPr fontId="1"/>
@@ -120,6 +120,16 @@
   </si>
   <si>
     <t>SNA_UC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実効税率は法人企業統計データより</t>
+    <rPh sb="0" eb="4">
+      <t>ジッコウゼイリツ</t>
+    </rPh>
+    <rPh sb="5" eb="11">
+      <t>ホウジンキギョウトウケイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2924,6 +2934,9 @@
       <c r="S8" s="1">
         <v>118.77844082873577</v>
       </c>
+      <c r="U8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
